--- a/src/attributions/attributions_ig_traj_453.xlsx
+++ b/src/attributions/attributions_ig_traj_453.xlsx
@@ -2140,22 +2140,22 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06965262371421381</v>
+        <v>0.2172447549739506</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0132067951477599</v>
+        <v>-0.03775690675533274</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05310844834014798</v>
+        <v>-0.1239852781600141</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -2164,37 +2164,37 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04591791322405216</v>
+        <v>0.3198337161255455</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01623528273736143</v>
+        <v>-0.08022915281717471</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.07677437657327492</v>
+        <v>-0.1416038535026611</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002278297006559302</v>
+        <v>-0.00526505540106578</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,40 +2203,40 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.001922188418225668</v>
+        <v>-0.02325712298631453</v>
       </c>
       <c r="X4" t="n">
-        <v>5.448076575841654e-12</v>
+        <v>-3.748364424199155e-11</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01947993184869364</v>
+        <v>-0.04584191858485273</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.03066154135110732</v>
+        <v>-0.1528624750881433</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.004235426966452045</v>
+        <v>-0.08351853453503433</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0131857595152292</v>
+        <v>0.06222665800710997</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,25 +2257,25 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01191853084078029</v>
+        <v>-0.04575472310642678</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.02419721448654926</v>
+        <v>-0.07518652513413636</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.09056969345535008</v>
+        <v>0.6962703472576671</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,79 +2284,79 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.002351787494214721</v>
+        <v>-0.1348219470708168</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.08211291476494845</v>
+        <v>-0.1491050221423267</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02233865973451455</v>
+        <v>-0.02609876772568996</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.03120009878822056</v>
+        <v>-0.08604057773159943</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.02200581126186145</v>
+        <v>-0.05811528119325234</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02527924845955864</v>
+        <v>0.09734258011174787</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.004905177572846247</v>
+        <v>0.1250832993755461</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01385494044593872</v>
+        <v>0.1079947709798323</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.042381330484443</v>
+        <v>0.3208011496758523</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,37 +2365,37 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01651827284042906</v>
+        <v>-0.1328563911694205</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.01423578080048319</v>
+        <v>-0.1838826095804996</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.02466569166017304</v>
+        <v>-0.1297138603936857</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0001486164489062312</v>
+        <v>0.01254590092396345</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03855459370986331</v>
+        <v>0.1151452004431389</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
@@ -2404,268 +2404,268 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.007457438885330226</v>
+        <v>-0.1933025479259437</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.01040422473354624</v>
+        <v>0.102108377586649</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.005822461686366765</v>
+        <v>0.05705153682581284</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
         <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01688526712682538</v>
+        <v>-0.1293904757024307</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.005163277025162915</v>
+        <v>-0.008918726024657602</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03967505526135616</v>
+        <v>0.1078603488475741</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01678691999249714</v>
+        <v>-0.008902037173511681</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01768122072368059</v>
+        <v>-0.1143949111264084</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.06368668214015714</v>
+        <v>0.05076336748979399</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.01126742494722356</v>
+        <v>-0.08149997865001914</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01534153253441296</v>
+        <v>0.0919256288108182</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.01223511385898438</v>
+        <v>0.137582986838546</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.005175023384943723</v>
+        <v>0.01031514208245848</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.004092087557110486</v>
+        <v>-0.02731117747769734</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.03289050972970652</v>
+        <v>-0.09010990924441759</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.0100562886045687</v>
+        <v>-0.08934470888080379</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0006590290531399393</v>
+        <v>-0.080369192563916</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0137314817850852</v>
+        <v>0.05969502512745942</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.00782115357997458</v>
+        <v>0.002238987523717299</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.003545606617250732</v>
+        <v>-0.1121478182518702</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.03973513648833167</v>
+        <v>0.08245621295172904</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01893077685402262</v>
+        <v>-0.1476691829832454</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.001363482948057746</v>
+        <v>-0.01960630923008163</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03724193435794861</v>
+        <v>0.09639201145877059</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01672543604043789</v>
+        <v>-0.1656164631663269</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01286796399207757</v>
+        <v>0.03767692226266613</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.00943632135172065</v>
+        <v>-0.02260221856258129</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.004157806154154446</v>
+        <v>0.09830811994334133</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.007975393088299058</v>
+        <v>0.002501462881602006</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03710564779001576</v>
+        <v>0.09692732252079135</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,13 +2674,13 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02186230022227217</v>
+        <v>-0.01495790397096928</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2689,10 +2689,10 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.01103051311706313</v>
+        <v>0.07670716877382366</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,43 +2709,43 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1402631533341512</v>
+        <v>0.2345514356196248</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.04912879048197314</v>
+        <v>-0.1010442134492659</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.04750837659328704</v>
+        <v>-0.05249739279684736</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09051486886840462</v>
+        <v>0.2405058944413528</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02648940313112126</v>
+        <v>-0.08032121364640546</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06413832112155535</v>
+        <v>-0.1019157653365255</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,22 +2760,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02128283347738671</v>
+        <v>0.0280511630536269</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.005219363906787938</v>
+        <v>-0.002209615995358874</v>
       </c>
       <c r="W5" t="n">
-        <v>0.009023482336106248</v>
+        <v>-0.004547349107108647</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2787,22 +2787,22 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.07072060223205257</v>
+        <v>-0.04817749620730993</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.005871792442933925</v>
+        <v>-0.07510685430060106</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.01044872076843468</v>
+        <v>-0.07582986551865689</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2811,58 +2811,58 @@
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01235426851502624</v>
+        <v>0.1077157492468253</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.05249862365867109</v>
+        <v>-0.03826380320792324</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.09150311279176528</v>
+        <v>0.06250160740684692</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3446418620553199</v>
+        <v>0.3486872970693812</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01700953759809372</v>
+        <v>-0.1962192200191785</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1116888641049259</v>
+        <v>-0.1584393380649127</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
@@ -2871,16 +2871,16 @@
         <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.02121397761067066</v>
+        <v>-0.01124442597441468</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.02988940695835018</v>
+        <v>-0.01696171689549637</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.08448486121409511</v>
+        <v>-0.02549790398940162</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,31 +2889,31 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.09300056740073318</v>
+        <v>-0.02109164751653288</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.05047132865002749</v>
+        <v>0.04725836895024822</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1120176387732719</v>
+        <v>0.07783945679314272</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,43 +2925,43 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1649324642928614</v>
+        <v>0.248901959635732</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.01191673198034119</v>
+        <v>-0.1510086022899194</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.02879173635911039</v>
+        <v>-0.01931328532757515</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.05288902792227426</v>
+        <v>-0.1265993398601487</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.02020383935825736</v>
+        <v>0.1018510592282475</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001175178729473224</v>
+        <v>0.02555038306061826</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
@@ -2970,7 +2970,7 @@
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,49 +2979,49 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.005590384767433862</v>
+        <v>-0.05322929169200533</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.02047943260782307</v>
+        <v>0.03579816345067879</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.05622776610803961</v>
+        <v>0.03129457433527731</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.02933029153234035</v>
+        <v>-0.1366820033082584</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0344016424220505</v>
+        <v>0.1187962033446716</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0143233921526459</v>
+        <v>0.02648950727407783</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3033,25 +3033,25 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.001436769962596578</v>
+        <v>-0.008113664243137191</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.01799160758896947</v>
+        <v>0.04475814513967349</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.0164584620475656</v>
+        <v>-0.09397486145756953</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>0</v>
@@ -3060,52 +3060,52 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.06195185423269622</v>
+        <v>-0.08701535433610533</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.02021394025621356</v>
+        <v>0.1022851841051144</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.009560833817958711</v>
+        <v>-0.04420249823603203</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0122477776896202</v>
+        <v>0.05031790697930141</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.02812076500092301</v>
+        <v>0.04693298617275144</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02401486906029487</v>
+        <v>-0.01663197371290008</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,19 +3114,19 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.0399580589533762</v>
+        <v>-0.07284535171571717</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.05663441606365035</v>
+        <v>0.09496615383908175</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.06963230544911359</v>
+        <v>0.02671548689751714</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.02545712271016326</v>
+        <v>-0.08708602174791846</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.04761359939506429</v>
+        <v>0.08320302383133431</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.001249441777564034</v>
+        <v>-0.03485821967131585</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>-0</v>
@@ -3165,73 +3165,73 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.03535632488407987</v>
+        <v>-0.1423290701897051</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.03527650774949386</v>
+        <v>0.1249442696449965</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0141269764997866</v>
+        <v>0.01359373365647693</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.04768732725384887</v>
+        <v>-0.05336413527467141</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.03612686861186749</v>
+        <v>0.01856066885279973</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.01871345285972179</v>
+        <v>0.05854388731251355</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.04802414125464317</v>
+        <v>-0.02545021372573101</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.007310134044962688</v>
+        <v>0.1868505320382722</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.04502327674953498</v>
+        <v>-0.07681283261513699</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
@@ -3246,28 +3246,28 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.03643824887127488</v>
+        <v>-0.1031775123663209</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.002662275058604669</v>
+        <v>0.0573010511520846</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03153556102038544</v>
+        <v>0.04122030643110757</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,10 +3287,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01242506609884394</v>
+        <v>0.02707541124388669</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.005953291223578763</v>
+        <v>-0.01328977999366624</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01847986701992851</v>
+        <v>0.07466533409763627</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0183594722283189</v>
+        <v>0.01704391851322167</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01357258504007898</v>
+        <v>-0.01984369599718409</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001459421199115091</v>
+        <v>-0.0009237173715095426</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001428408144818291</v>
+        <v>-0.009745131528855937</v>
       </c>
       <c r="X6" t="n">
-        <v>7.980461131626318e-12</v>
+        <v>5.069369833808241e-12</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01550556886252513</v>
+        <v>-0.0247421425904471</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02153304075178343</v>
+        <v>-0.0676561467090776</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.004111671910285146</v>
+        <v>-0.02412788052078279</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,49 +3386,49 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0066487938371425</v>
+        <v>0.01019878781272478</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01554110155979732</v>
+        <v>-0.007496379745938913</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.006543301272340176</v>
+        <v>-0.03663848136957595</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.06315701889423338</v>
+        <v>0.1392622727777732</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.008069755532742248</v>
+        <v>-0.0321215951271347</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01575980148389394</v>
+        <v>-0.021026079169775</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3437,10 +3437,10 @@
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.005926090729368482</v>
+        <v>-0.01348681463988576</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.02088801568923125</v>
+        <v>-0.01965030476288157</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.002347377510720586</v>
+        <v>-0.00720033445286524</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,10 +3464,10 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02604697749760845</v>
+        <v>0.0271246210296994</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
@@ -3476,25 +3476,25 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0126362358528689</v>
+        <v>0.05134016189273854</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.009684679261324526</v>
+        <v>0.03595128661765075</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.02031413403598212</v>
+        <v>0.05835195910991028</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01575623471081897</v>
+        <v>-0.002392398945668208</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01606884136564738</v>
+        <v>-0.04187152936320424</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,25 +3521,25 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.005991232668775134</v>
+        <v>-0.01458833037638711</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0005064918714978078</v>
+        <v>-0.001200130150223488</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.006841301302198279</v>
+        <v>0.02864256706974729</v>
       </c>
       <c r="CJ6" t="n">
         <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
@@ -3548,49 +3548,49 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0005522331387722264</v>
+        <v>-0.03147500423215389</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.004815076043533315</v>
+        <v>0.05361160005256081</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.009843538713509882</v>
+        <v>0.0215425267478122</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.001532137412975494</v>
+        <v>-0.01898451486293274</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.001059880558136619</v>
+        <v>-0.004838297383208386</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.009113863484528228</v>
+        <v>0.02286760899575708</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3599,22 +3599,22 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.007804599131386967</v>
+        <v>-0.01054733680848532</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0002270179709576944</v>
+        <v>-0.001924077061105442</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.008548981489761973</v>
+        <v>0.0007387645050977864</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,31 +3623,31 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.004401794861962805</v>
+        <v>-0.01128382841580131</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01409363852646035</v>
+        <v>0.0002330495199352185</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.0009941877093691254</v>
+        <v>0.02847703843281502</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,103 +3656,103 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.004803730462906075</v>
+        <v>-0.01733674777993086</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.00918932724823469</v>
+        <v>0.002720390028298034</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.004227455279006476</v>
+        <v>0.02117280296978345</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0008439952123947626</v>
+        <v>-0.0197316231458473</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0002320257289284867</v>
+        <v>-0.02321263158946219</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.007799346900658764</v>
+        <v>-0.0006396277859103351</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.00262559915194264</v>
+        <v>-0.003888711652016463</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01349191189659547</v>
+        <v>0.0006642232031159704</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03318188055261515</v>
+        <v>0.01837334382255984</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0005930161968536497</v>
+        <v>-0.0246566438749954</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.001164543396922449</v>
+        <v>-0.0101234017092286</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0108466985666311</v>
+        <v>0.01754548966551739</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,22 +3761,22 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.008321278001343694</v>
+        <v>-0.02878607181811819</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01331183297287282</v>
+        <v>0.01732578030132512</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01818152631671502</v>
+        <v>-0.01145356730190105</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.001312256177006958</v>
+        <v>0.02871219553400421</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.006195928766814581</v>
+        <v>0.001820597968506677</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.002010481412058339</v>
+        <v>-0.03134339042851161</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3815,10 +3815,10 @@
         <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01881500729147983</v>
+        <v>0.01433592579815393</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
@@ -3830,10 +3830,10 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.0004130896055308887</v>
+        <v>0.0139610440199983</v>
       </c>
       <c r="GE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1161171007030521</v>
+        <v>0.06163419818885624</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,25 +3856,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.007454846663167947</v>
+        <v>-0.02866431748545425</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01137906764179183</v>
+        <v>-0.004435739116207757</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05904591585960912</v>
+        <v>0.0959019293774762</v>
       </c>
       <c r="L7" t="n">
         <v>-0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06413203472583247</v>
+        <v>-0.0357774506936383</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,52 +3892,52 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.02957352737527708</v>
+        <v>-0.007973831697538155</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01315883299703815</v>
+        <v>-0.004507848208321096</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.005369576551095501</v>
+        <v>-0.01428892070043223</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.675737786816843e-12</v>
+        <v>-1.512439440084558e-12</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04409505660060739</v>
+        <v>-0.01754402236488705</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03406352979849904</v>
+        <v>-0.02290854177630602</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01352416401325335</v>
+        <v>-0.0005207831293611341</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0285094479214747</v>
+        <v>0.03135388823641832</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01786107287736121</v>
+        <v>-0.00932574437224077</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01938127469321971</v>
+        <v>-0.00530651351924731</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2087284200287786</v>
+        <v>0.1184464375463839</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.09369622605038209</v>
+        <v>-0.02302924234815486</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.001535302980103801</v>
+        <v>0.01322868268727528</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.00651775061478526</v>
+        <v>-0.006284135729716994</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,79 +4018,79 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.06439493252387811</v>
+        <v>-0.02308489731795241</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.004500013008519102</v>
+        <v>-0.003235997433419402</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03341117496132391</v>
+        <v>0.01669992955393194</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08817714020607892</v>
+        <v>0.04527160510583954</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02942284075847584</v>
+        <v>0.01549042527707998</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1069432036434638</v>
+        <v>0.06533968106799659</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.01606320361967048</v>
+        <v>-0.02771452669376186</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.002624615642048421</v>
+        <v>-0.02115561917862766</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0288202447709403</v>
+        <v>-0.02848837748088434</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0001620767091287814</v>
+        <v>0.01103578613553557</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.03025057956595246</v>
+        <v>0.014568240553066</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01711400597859648</v>
+        <v>-0.03351686100738316</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.007127718811957289</v>
+        <v>0.005814832206695607</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.008122279364480926</v>
+        <v>0.01352795764829133</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.02367596032877793</v>
+        <v>-0.02945568735151479</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,133 +4153,133 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.003929270086939453</v>
+        <v>0.006134100013769008</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.03194045087277503</v>
+        <v>0.01362030422181335</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.09313311778348607</v>
+        <v>-0.0226615298380385</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03359484218654588</v>
+        <v>-0.01405912099707589</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.01557584022725964</v>
+        <v>-0.007905850762684831</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.001789446622156118</v>
+        <v>-0.02273482934713726</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.00173912143378541</v>
+        <v>0.0110450505004678</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.007625757581998707</v>
+        <v>-0.03479246953200928</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.005878414134021429</v>
+        <v>0.01054941532148871</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.02349085428539276</v>
+        <v>0.008463253571686978</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.01308885383546396</v>
+        <v>-0.01055690439931422</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.003222057714930026</v>
+        <v>-0.02316812337099833</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.02399224766819068</v>
+        <v>0.001549873358913579</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.03109475537076417</v>
+        <v>0.006002883859277599</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.04204236755861852</v>
+        <v>-0.005476256151566057</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.003888980288651529</v>
+        <v>0.006289228720743823</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.01010547251567656</v>
+        <v>0.008382652303069183</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.03368984787437714</v>
+        <v>-0.03397185693942503</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.005844099718807129</v>
+        <v>0.002836515800284795</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,40 +4327,40 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.018694573387476</v>
+        <v>0.01463318809550707</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03929705326491671</v>
+        <v>-0.02091211348941297</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.0284574729929021</v>
+        <v>0.01065911190040715</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0116095560653988</v>
+        <v>0.04782761017673067</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.0619878757214444</v>
+        <v>0.01052630380498668</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,28 +4369,28 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.005042285320660026</v>
+        <v>-0.02174021671001826</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-0.0005387351663911457</v>
+        <v>0.002126025769599227</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03254117220803813</v>
+        <v>-0.01489150077579584</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03659005549313916</v>
+        <v>0.002721086062823072</v>
       </c>
     </row>
     <row r="8">
@@ -4982,25 +4982,25 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3019212841299535</v>
+        <v>0.09052103066706561</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1244636318331575</v>
+        <v>-0.1620724754009127</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.001896006330799194</v>
+        <v>-0.01536131760229151</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5009,19 +5009,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2093191549904211</v>
+        <v>0.07680868938394167</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1516859587528174</v>
+        <v>-0.2279076142160478</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.07552756366442445</v>
+        <v>-0.0630947558409581</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5036,28 +5036,28 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.05608637754124651</v>
+        <v>0.05762099312903692</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001655122229820161</v>
+        <v>-0.01370580828374247</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01126624591136036</v>
+        <v>-0.06331615026973368</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>-0</v>
@@ -5066,19 +5066,19 @@
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1330184137875475</v>
+        <v>-0.01340480469671162</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.05016931469978424</v>
+        <v>-0.08115676059348437</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01251945208978315</v>
+        <v>-0.06936212262677043</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
@@ -5087,58 +5087,58 @@
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01661356338387513</v>
+        <v>0.1273304480056859</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.0464518451982801</v>
+        <v>-0.07564384403024405</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.09022803150748752</v>
+        <v>0.03740483277379519</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4535976227296254</v>
+        <v>0.2205487702273443</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.03342418362059519</v>
+        <v>-0.1119647368817928</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.2002718008022514</v>
+        <v>-0.3572584111307794</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
@@ -5147,16 +5147,16 @@
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0140132442171513</v>
+        <v>-0.07835414247323345</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.08396154068161647</v>
+        <v>-0.03327543469732974</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1572969478140629</v>
+        <v>0.04529544589673842</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1284677850230491</v>
+        <v>0.05267380316677231</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01935220917745772</v>
+        <v>0.02349836394892471</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1508062703794752</v>
+        <v>-0.01147327927199365</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2339231213351282</v>
+        <v>0.1891048473422581</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.009652962032730878</v>
+        <v>-0.1994742668830502</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.06225120943805748</v>
+        <v>-0.1200051974760054</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5225,19 +5225,19 @@
         <v>-0</v>
       </c>
       <c r="CD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.08244923423171428</v>
+        <v>-0.02344127347982645</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.003930233467063867</v>
+        <v>0.1369178090250502</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.02283573825772168</v>
+        <v>0.03740930450388953</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
         <v>-0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5255,16 +5255,16 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.04374653691585031</v>
+        <v>-0.009929929485883369</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.0808776704476345</v>
+        <v>0.1937742637871094</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.04043984574841659</v>
+        <v>0.1291925168560401</v>
       </c>
       <c r="CR9" t="n">
         <v>0</v>
@@ -5273,55 +5273,55 @@
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.05428621807951961</v>
+        <v>-0.006434719491703167</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02429747025948435</v>
+        <v>0.1514928288363036</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.004967881893598342</v>
+        <v>0.05566013458333183</v>
       </c>
       <c r="DA9" t="n">
         <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01586609896450627</v>
+        <v>0.00599782580476247</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.02226769682008138</v>
+        <v>0.02500728082614451</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.008348801943286415</v>
+        <v>-0.007849884265711553</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
@@ -5333,46 +5333,46 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.06405152593805531</v>
+        <v>-0.04936261037793168</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.02089221867776788</v>
+        <v>0.07910102701825178</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01962201658198517</v>
+        <v>0.001569453591740367</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.02385587633704251</v>
+        <v>0.03985229021578172</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.0231926933514335</v>
+        <v>0.05600982354475189</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.03052183031158026</v>
+        <v>-0.09260499677114775</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
@@ -5381,25 +5381,25 @@
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.01768728118725849</v>
+        <v>0.04892854595658482</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.03296438687643364</v>
+        <v>0.1109919921931838</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04271602340955431</v>
+        <v>0.04288348088001105</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
@@ -5408,31 +5408,31 @@
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.08083830177160867</v>
+        <v>-0.03370738782635065</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.04734034503756699</v>
+        <v>-0.1343492251320282</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.002797138610991398</v>
+        <v>-0.001179778815685768</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5441,97 +5441,97 @@
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.06738043758584933</v>
+        <v>-0.01987804580182272</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.01253975774768924</v>
+        <v>0.1691241166092122</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.008958487328733644</v>
+        <v>0.03322204516179506</v>
       </c>
       <c r="FC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0306468807951857</v>
+        <v>0.02361170399682207</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.03580579225431035</v>
+        <v>0.01621846274368375</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.02433709717556653</v>
+        <v>-0.02637202757135609</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
         <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.03425321492073131</v>
+        <v>0.05189243499758008</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.04175246996048487</v>
+        <v>0.1231362187774974</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.04690119223899062</v>
+        <v>-0.1670230606193775</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
         <v>-0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.03238765441937098</v>
+        <v>-0.00854317993123099</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.07041884746163696</v>
+        <v>0.1064583283425375</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
@@ -5551,19 +5551,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4015164711808807</v>
+        <v>0.167985521258226</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.162243735278075</v>
+        <v>-0.3807229323845323</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1298679122191862</v>
+        <v>-0.05303578636698852</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,25 +5572,25 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.002196563933134524</v>
+        <v>0.01450679981203641</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2866420476512556</v>
+        <v>0.05392314599959501</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1650723141899183</v>
+        <v>-0.5611176147227034</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2338162230602431</v>
+        <v>-0.1691884910635112</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,88 +5599,88 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.773843992507836e-05</v>
+        <v>0.007532652635448137</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1194001429794099</v>
+        <v>0.1076368247591064</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.04146989523935434</v>
+        <v>-0.1061936870364082</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.009577813371606731</v>
+        <v>-0.184490348725769</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.165141869562668e-11</v>
+        <v>9.153863379113565e-12</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.07535709907618832</v>
+        <v>-0.06947348259294334</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0719574550843427</v>
+        <v>-0.0672156921913218</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.04510699066944255</v>
+        <v>-0.1534637372504252</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01408999266914062</v>
+        <v>0.02016047965669047</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.03042748983655356</v>
+        <v>0.2605458453001208</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.06682039923425173</v>
+        <v>-0.1368501506979959</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.07963133236139716</v>
+        <v>0.1306269124417437</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0188317380854795</v>
+        <v>0.02550113816303586</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,25 +5689,25 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6171267101276915</v>
+        <v>0.3643552176977319</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.01504940877566782</v>
+        <v>-0.2603391996351306</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1780355768034943</v>
+        <v>-0.6159894383654629</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.07590058188381982</v>
+        <v>-0.04052465272244211</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.02159293685063407</v>
+        <v>-0.13148559164541</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.07999834299163916</v>
+        <v>-0.02386249143327265</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.3451410122237681</v>
+        <v>-0.03803160826438509</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-1.025408752838349e-11</v>
+        <v>4.419321513280147e-11</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.2048410783397344</v>
+        <v>0.02416295453707074</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.123932774274905</v>
+        <v>0.1799940230185386</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.134053709600903</v>
+        <v>-0.1131724462318108</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.03255796661519469</v>
+        <v>-0.03164229518817984</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,106 +5770,106 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2983067381313633</v>
+        <v>0.2508370578450762</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01299885167966509</v>
+        <v>-0.4587242332428235</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.03914353371971967</v>
+        <v>-0.3195863075609337</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.003081441608691223</v>
+        <v>-0.03447878171874384</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.09855116117914485</v>
+        <v>-0.04550965557738917</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.03411704048279777</v>
+        <v>0.331164050221967</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.006197954328820997</v>
+        <v>0.05924693693685427</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ10" t="n">
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.002073265252340078</v>
+        <v>-0.09930461677559813</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.06147291244789958</v>
+        <v>0.01163545688653395</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.0759582108131692</v>
+        <v>0.2307943926526271</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.009006737943174912</v>
+        <v>0.3798480422147974</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.04758675488980163</v>
+        <v>0.02025822747621757</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.06382970467639522</v>
+        <v>-0.03567147768128527</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.06542701278397187</v>
+        <v>0.3585315019121271</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-6.167964947584231e-05</v>
+        <v>0.07663652377169193</v>
       </c>
       <c r="DA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0001098689537699077</v>
+        <v>-0.07318664835943596</v>
       </c>
       <c r="DD10" t="n">
         <v>-0</v>
@@ -5878,25 +5878,25 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.07308593494924069</v>
+        <v>-0.06219557405376034</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.05179340999601858</v>
+        <v>0.1133125579343868</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.0004495546668951363</v>
+        <v>0.01342832013705214</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001840681708277136</v>
+        <v>-0.1071280440755547</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
@@ -5905,16 +5905,16 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.09784657496771371</v>
+        <v>-0.004734000348395469</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.02541881010834486</v>
+        <v>0.13947716007416</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.03446287494005714</v>
+        <v>-0.07210931934928998</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,7 +5923,7 @@
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.006357608897688938</v>
+        <v>0.1855052201476143</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,16 +5932,16 @@
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.01928468725248561</v>
+        <v>0.05639814477634211</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.02354472591987242</v>
+        <v>0.1503047984309671</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.05665129497128161</v>
+        <v>-0.1260490675401939</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
@@ -5950,106 +5950,106 @@
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.0107638436428869</v>
+        <v>0.3047575687226274</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.05257464633749249</v>
+        <v>0.08515169632103688</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.06985138506152817</v>
+        <v>0.251702014750998</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04407883599778439</v>
+        <v>0.06324996358219967</v>
       </c>
       <c r="EK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.03631718298696239</v>
+        <v>-0.07062578016520869</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.08520831813968727</v>
+        <v>-0.06842000213959502</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.1011005925179925</v>
+        <v>0.3085281774098612</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.03888338219626104</v>
+        <v>0.01749237177252435</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.01438631126932967</v>
+        <v>-0.05854536550755617</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.0759754629482359</v>
+        <v>-0.05658563304947768</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.05499050605453597</v>
+        <v>0.4007234133478521</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.02074012071859481</v>
+        <v>0.08407966463068063</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0.0004590666858990546</v>
+        <v>-0.09869539888814388</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.04837642302047352</v>
+        <v>-0.03682143758996388</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.06415811631540622</v>
+        <v>-0.190035153161607</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03679165762082445</v>
+        <v>0.002953149906384522</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
@@ -6058,49 +6058,49 @@
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.002050615440955606</v>
+        <v>-0.08549138331242048</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.08536523914452887</v>
+        <v>0.1538753368603839</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.05497083802582022</v>
+        <v>0.2532004744178417</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.09253670187239249</v>
+        <v>-0.1734093848556051</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>2.300604822874316e-05</v>
+        <v>-0.2632459918269195</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1059026616373485</v>
+        <v>0.02523944667699484</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.02873256944932742</v>
+        <v>0.2157953124584444</v>
       </c>
       <c r="GC10" t="n">
         <v>-0</v>
@@ -6112,7 +6112,7 @@
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.02947763973571986</v>
+        <v>-0.08874080699831471</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,19 +6123,19 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2962127910196322</v>
+        <v>0.494004580250791</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0794314827713265</v>
+        <v>-0.09864761834638316</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3251552092915581</v>
+        <v>-0.3290378601252535</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2629837857579844</v>
+        <v>0.7795725181737319</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.07159152094960258</v>
+        <v>-0.2180086703888332</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3179368627319411</v>
+        <v>-0.357182473035687</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -6177,46 +6177,46 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03523435031640208</v>
+        <v>0.1715987913316617</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.02463843383928913</v>
+        <v>-0.2031349458835678</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004668410649388662</v>
+        <v>-0.02568927931101627</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.03675971385235492</v>
+        <v>0.03403126634182452</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.009395998632068097</v>
+        <v>-0.5087357999986366</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.005707230839108877</v>
+        <v>-0.01114466899747255</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,115 +6231,115 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.05870138376722164</v>
+        <v>0.1145240429066026</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.002304377691093237</v>
+        <v>-0.1769459908183068</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.06017337604118368</v>
+        <v>-0.06566667451651836</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.3028903815037773</v>
+        <v>1.081038540004021</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.01307273160712979</v>
+        <v>-0.45859529560838</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.158608514226485</v>
+        <v>-0.2012063478263005</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.10473886162177</v>
+        <v>-0.1659824116236875</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1292153063364998</v>
+        <v>-0.08701031161595164</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.1541380521351499</v>
+        <v>-0.06627233193753605</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1386154872188016</v>
+        <v>0.2680498354807915</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.03976924489844725</v>
+        <v>0.2248971309661246</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01588841471186974</v>
+        <v>0.05485766225851931</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1493340254400462</v>
+        <v>0.616384687466628</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,40 +6348,40 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.02029345586095235</v>
+        <v>-0.2127857909393576</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.07543376336430127</v>
+        <v>-0.193570523431553</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.06107299957612145</v>
+        <v>-0.2071184879167658</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.005462934584520061</v>
+        <v>0.1260653336424633</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.07567569821855132</v>
+        <v>0.1269378082366381</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,19 +6393,19 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.02527754020166652</v>
+        <v>-0.3237183423588251</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.01079361677557619</v>
+        <v>0.2881046795091656</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.0134062306392451</v>
+        <v>0.06473437536757991</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
@@ -6420,19 +6420,19 @@
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.04092305421946318</v>
+        <v>-0.186341655722113</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.008836695591403541</v>
+        <v>0.05579303962278612</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.07393416580392463</v>
+        <v>0.1296840915197607</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
@@ -6444,22 +6444,22 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.05205553808121168</v>
+        <v>-0.07245982409741226</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.03469555737188169</v>
+        <v>-0.1576446767244877</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.006543343349842912</v>
+        <v>-0.06219671836580573</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,25 +6468,25 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.02403335065064489</v>
+        <v>-0.1267789922815336</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.03074879820604255</v>
+        <v>-0.04674787224874739</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.03800906293009364</v>
+        <v>-0.07535333394894832</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6495,58 +6495,58 @@
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.01627373183585723</v>
+        <v>0.1183234608264528</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.01362330268880633</v>
+        <v>-0.1163939389222803</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.01727799743227545</v>
+        <v>0.003957960572214821</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
         <v>-0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.02206748883148681</v>
+        <v>-0.004510550835073699</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.006243774999739808</v>
+        <v>-0.01393433340531596</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.06133942838990441</v>
+        <v>0.1291013154898347</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>0</v>
@@ -6555,19 +6555,19 @@
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.01439953548536112</v>
+        <v>0.02692446270187302</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01210939280857864</v>
+        <v>-0.1275861095541629</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0547082893706542</v>
+        <v>0.09913747458739038</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
@@ -6579,55 +6579,55 @@
         <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.03976921609440331</v>
+        <v>-0.2392306110066953</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0107622551996117</v>
+        <v>0.08030363900992557</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.07553593964051231</v>
+        <v>0.1176982698101644</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.03037441473876131</v>
+        <v>-0.2056606115979984</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.01773561569528527</v>
+        <v>0.2640459215959304</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.04365721442228479</v>
+        <v>0.01339316706959876</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,46 +6636,46 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.03122763092286335</v>
+        <v>0.1394840548136519</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.03734237874889076</v>
+        <v>-0.2810668095705221</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.04304409050911572</v>
+        <v>0.1506258645918039</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.03442641838414884</v>
+        <v>-0.1316148406783702</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.03868904628827099</v>
+        <v>0.1458349191815676</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2893308073205843</v>
+        <v>0.6205639602032749</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1419535223640453</v>
+        <v>-0.3355285061493603</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04678776521098074</v>
+        <v>-0.07038510898842233</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6716,19 +6716,19 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2223878588418357</v>
+        <v>0.6472402726388585</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1490420652592066</v>
+        <v>-0.456084118629613</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.09850853879884507</v>
+        <v>-0.2487799843675761</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6743,22 +6743,22 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.10496066100216</v>
+        <v>0.1216447699522522</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.008336219470908466</v>
+        <v>-0.08100988473055347</v>
       </c>
       <c r="W12" t="n">
-        <v>0.05189868317724598</v>
+        <v>-0.1414466993888769</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,79 +6770,79 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1226706867455125</v>
+        <v>-0.1499977049219836</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.02622097773023647</v>
+        <v>-0.1879693236213647</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.01358927329651911</v>
+        <v>-0.1957531916526471</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0261808401336431</v>
+        <v>0.2430460597951589</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.03596231415873668</v>
+        <v>-0.1532640655636717</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.05894296015706968</v>
+        <v>0.09941293910365377</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3509165762832935</v>
+        <v>0.485143402058943</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.006030863900176995</v>
+        <v>-0.1554224521367465</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.09363614144551978</v>
+        <v>-0.4600237727672786</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -6854,16 +6854,16 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02700411312040913</v>
+        <v>0.007954104663604271</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.09197620898769655</v>
+        <v>-0.1156791288182751</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1872055844340971</v>
+        <v>0.02751783186175305</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,52 +6881,52 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.09649162602644107</v>
+        <v>0.004992358369194344</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0413918121101997</v>
+        <v>0.05904979395586835</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1005156897292799</v>
+        <v>0.07473951761928922</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1706785228081994</v>
+        <v>0.4153431825179178</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.005380969536502351</v>
+        <v>-0.214402273895481</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.06797186652176784</v>
+        <v>-0.1303032518557891</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,19 +6935,19 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.07397288827463021</v>
+        <v>-0.2062428118848894</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.008558510514092793</v>
+        <v>0.2199117425909468</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.007520654568285647</v>
+        <v>0.02821791270633977</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
         <v>-0</v>
@@ -6962,19 +6962,19 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.03825970163358847</v>
+        <v>-0.04346765628129853</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.04639469223090675</v>
+        <v>0.2964427966575159</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.02109520902193884</v>
+        <v>0.08473736812587195</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,25 +6989,25 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.04532410667850405</v>
+        <v>-0.1856430332442287</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.02323054925670109</v>
+        <v>0.235862983079838</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.003467646910161157</v>
+        <v>0.06318712540208761</v>
       </c>
       <c r="DA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,43 +7016,43 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.05613217223555436</v>
+        <v>-0.1456534679010801</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01596265549001635</v>
+        <v>0.04061363827738289</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.02080380292310339</v>
+        <v>-0.1267562417965584</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.05155162770062629</v>
+        <v>-0.147622859665583</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.00398404685740763</v>
+        <v>0.1177086895701081</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.03611025494201275</v>
+        <v>0.0239090895775671</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
@@ -7061,34 +7061,34 @@
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.02856591306200486</v>
+        <v>-0.01128906915435487</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.01819180843771786</v>
+        <v>-0.07062033486888138</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.02034392112056498</v>
+        <v>0.001373546122757307</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
@@ -7097,52 +7097,52 @@
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02632004846844499</v>
+        <v>-0.1179286870054089</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.05174326804297629</v>
+        <v>0.1863050547665308</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.04890421909466904</v>
+        <v>0.04615405549020953</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.0599284100008774</v>
+        <v>-0.1417578120283744</v>
       </c>
       <c r="EQ12" t="n">
         <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.02615693650730194</v>
+        <v>0.1816775316742861</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.04746573685542603</v>
+        <v>-0.05524862090641305</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
@@ -7151,22 +7151,22 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.0564108906613917</v>
+        <v>-0.2196457702003873</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.02603269551359643</v>
+        <v>0.2547878418832686</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.007988088297983698</v>
+        <v>0.01644215646179779</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7178,16 +7178,16 @@
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.02457064156264356</v>
+        <v>-0.1414170835309113</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.03746725420537458</v>
+        <v>0.09958505667260792</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.05215636501321517</v>
+        <v>-0.01540138344004897</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7199,69 +7199,69 @@
         <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.02086756647181548</v>
+        <v>-0.006863205522971719</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.02031375279636649</v>
+        <v>0.2228494202962294</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.02096051778953616</v>
+        <v>0.06057427010144951</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.01885565083916371</v>
+        <v>-0.1432927680947959</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.0656093774582745</v>
+        <v>0.160010741865401</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.4400302211912957</v>
+        <v>-0.2165906821380787</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
@@ -7270,10 +7270,10 @@
         <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1461241172552608</v>
+        <v>-0.008581866336434657</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7890443033078912</v>
+        <v>0.3178129012626952</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
@@ -7285,22 +7285,22 @@
         <v>-0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3324966261368732</v>
+        <v>-0.2709181503864927</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.009800255643548566</v>
+        <v>0.06498811939487208</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7435162744535142</v>
+        <v>0.3204943841950541</v>
       </c>
       <c r="P13" t="n">
         <v>-0</v>
@@ -7312,49 +7312,49 @@
         <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.02852553755507251</v>
+        <v>-0.1202322284079169</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>-0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.185601812712733</v>
+        <v>0.169838718989137</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1072440994968036</v>
+        <v>0.05251764841172159</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.03382671661840421</v>
+        <v>-0.005295025369761642</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.03234939687559153</v>
+        <v>0.2901872372760413</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.06251031936358561</v>
+        <v>0.196789573944423</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,22 +7369,22 @@
         <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.05538661300786257</v>
+        <v>-0.114642748458964</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
         <v>-0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.0322000688477382</v>
+        <v>-0.06055465499386326</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.1227122301420223</v>
+        <v>0.1330314526364324</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -7396,7 +7396,7 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.3931463321596582</v>
+        <v>-0.5208969442703992</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -7405,25 +7405,25 @@
         <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.2323413491674978</v>
+        <v>0.05699969459624027</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.5890196543049772</v>
+        <v>0.1828626630686929</v>
       </c>
       <c r="AZ13" t="n">
         <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0.212996368384224</v>
+        <v>0.1264766761214474</v>
       </c>
       <c r="BE13" t="n">
         <v>-0</v>
@@ -7432,40 +7432,40 @@
         <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.05136683520176594</v>
+        <v>0.1971383145837929</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.2075023442196922</v>
+        <v>0.1441581488052335</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
         <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.1941601695485171</v>
+        <v>-0.02233873469021851</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.1204997837809557</v>
+        <v>-0.09761099612356548</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01807009386510154</v>
+        <v>-0.00744582949964452</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7477,22 +7477,22 @@
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0.2293525259763025</v>
+        <v>-0.3263272466155183</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
         <v>-0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1399621449791268</v>
+        <v>0.08716743418209764</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.3235731351534769</v>
+        <v>0.2247024524476336</v>
       </c>
       <c r="CA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="n">
         <v>0</v>
@@ -7504,49 +7504,49 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.1022964031386092</v>
+        <v>0.1045230469906469</v>
       </c>
       <c r="CF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG13" t="n">
         <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.0230976691802364</v>
+        <v>-0.03151522569831839</v>
       </c>
       <c r="CI13" t="n">
-        <v>-0.1562743672663109</v>
+        <v>-0.109953513617096</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
         <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.03138869183741642</v>
+        <v>0.1627302366782908</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.1220698926590878</v>
+        <v>-0.2239750600455154</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.02269890678759298</v>
+        <v>-0.1370233298474724</v>
       </c>
       <c r="CS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT13" t="n">
         <v>0</v>
@@ -7558,22 +7558,22 @@
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.07014813702145432</v>
+        <v>0.09757877956074286</v>
       </c>
       <c r="CX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY13" t="n">
         <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.02842803018107314</v>
+        <v>-0.01930886497642678</v>
       </c>
       <c r="DA13" t="n">
-        <v>-0.1428503779882702</v>
+        <v>-0.1003524687488619</v>
       </c>
       <c r="DB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
@@ -7585,49 +7585,49 @@
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.03522274326580417</v>
+        <v>0.03566141734417238</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
         <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.1937875658370731</v>
+        <v>0.1071668408987398</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.03678692978627917</v>
+        <v>0.0006288677120105368</v>
       </c>
       <c r="DK13" t="n">
         <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.01263993120250317</v>
+        <v>0.06313262208822067</v>
       </c>
       <c r="DP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.03452392471642902</v>
+        <v>0.02462543252895269</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.01358223511800464</v>
+        <v>-0.08546465506585335</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
@@ -7636,49 +7636,49 @@
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.00946477032141777</v>
+        <v>-0.05757944964905756</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.02252276054972439</v>
+        <v>0.06308168337949935</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.1092765623424978</v>
+        <v>-0.0578160351298208</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.07556564415788805</v>
+        <v>0.02419588469047804</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
         <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.09070887990300125</v>
+        <v>0.03284107378020697</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0.1191578180235507</v>
+        <v>-0.0362695962696532</v>
       </c>
       <c r="EL13" t="n">
         <v>0</v>
@@ -7690,52 +7690,52 @@
         <v>0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.02744778016513771</v>
+        <v>-0.00283750034695207</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
         <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.0101719222262325</v>
+        <v>0.03108869083900959</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0.1396816561472966</v>
+        <v>-0.0817903930226082</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.06036844226931955</v>
+        <v>0.1180490028249907</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.07638419469111281</v>
+        <v>-0.02206921370753663</v>
       </c>
       <c r="FC13" t="n">
-        <v>-0.1457296525508723</v>
+        <v>-0.104397090985625</v>
       </c>
       <c r="FD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
@@ -7747,7 +7747,7 @@
         <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.06918441783419628</v>
+        <v>0.1491092241008986</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,25 +7756,25 @@
         <v>0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.01837688591148355</v>
+        <v>-0.06314786864019561</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02095011276292382</v>
+        <v>0.02228865680884227</v>
       </c>
       <c r="FM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.005895431789591535</v>
+        <v>-0.04428354181016673</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
@@ -7783,10 +7783,10 @@
         <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01979911303407366</v>
+        <v>0.02648264502516235</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.04485267642548387</v>
+        <v>0.04697759584587345</v>
       </c>
       <c r="FV13" t="n">
         <v>0</v>
@@ -7795,13 +7795,13 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.03347583013994021</v>
+        <v>0.06385253576753863</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,13 +7813,13 @@
         <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.03583740225635566</v>
+        <v>-0.003461025190919671</v>
       </c>
       <c r="GE13" t="n">
         <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>-0</v>
@@ -7827,7 +7827,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2127481818162456</v>
+        <v>0.1820868116404855</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -7836,25 +7836,25 @@
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1213452895671792</v>
+        <v>-0.2989566295082255</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1442763001557124</v>
+        <v>0.1501311534043056</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
         <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2153879649628282</v>
+        <v>0.1242091981658874</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -7863,25 +7863,25 @@
         <v>-0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.04883055807025742</v>
+        <v>-0.3911940618787668</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08139647994910056</v>
+        <v>0.08088917127264002</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02999942266900436</v>
+        <v>-0.0174890158040673</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -7890,40 +7890,40 @@
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.06181685061295922</v>
+        <v>-0.05008096444047652</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04740348320885432</v>
+        <v>-0.09057651772862954</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>-0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.02435029733487662</v>
+        <v>0.05104336633364986</v>
       </c>
       <c r="AC14" t="n">
         <v>-0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.0128775452128222</v>
+        <v>0.06729077181760416</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.007291442668956003</v>
+        <v>0.2639042625378563</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -7932,49 +7932,49 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0009876712400837115</v>
+        <v>0.04776198746971076</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.0151127693234958</v>
+        <v>-0.1583115555908282</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.06589065669835305</v>
+        <v>0.07281410993188218</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.1143883016956932</v>
+        <v>-0.105579273568998</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.05106196232588504</v>
+        <v>-0.3878022344848796</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1637094856704814</v>
+        <v>-0.007108756378489759</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
@@ -7989,7 +7989,7 @@
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.1184517735411994</v>
+        <v>0.1722247511198576</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -7998,37 +7998,37 @@
         <v>-0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.01703979127276205</v>
+        <v>0.253267085789173</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.08761464013488872</v>
+        <v>0.235604142592459</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.02245733433503399</v>
+        <v>-0.02725143334049337</v>
       </c>
       <c r="BM14" t="n">
         <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.01721859463317704</v>
+        <v>0.00866922115925582</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0858856748505327</v>
+        <v>-0.1106126519872101</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -8037,25 +8037,25 @@
         <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.05186853012291872</v>
+        <v>-0.07733980043878599</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.002413317766101937</v>
+        <v>-0.3059389286532656</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.08014564655202941</v>
+        <v>-0.07416123678708315</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -8064,25 +8064,25 @@
         <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0.04171991599811762</v>
+        <v>-0.06756851683023335</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.01664242001583374</v>
+        <v>0.1130726601047349</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.03108536949131906</v>
+        <v>-0.04973943971068842</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
@@ -8097,46 +8097,46 @@
         <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0.02003297917815343</v>
+        <v>0.02643852241755306</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.08086158364985026</v>
+        <v>0.1298124110262103</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.09596145660160081</v>
+        <v>-0.09289987475637576</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0.03252811021633836</v>
+        <v>-0.06161136108436876</v>
       </c>
       <c r="CW14" t="n">
         <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.001530118247315277</v>
+        <v>0.1150627857850047</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.02307518383511102</v>
+        <v>-0.02802864874725379</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
@@ -8151,7 +8151,7 @@
         <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0.01613871915039517</v>
+        <v>-0.01580293694054898</v>
       </c>
       <c r="DF14" t="n">
         <v>-0</v>
@@ -8160,10 +8160,10 @@
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.05611999808322592</v>
+        <v>0.1305031003857235</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.02227689626098308</v>
+        <v>-0.01480581711724752</v>
       </c>
       <c r="DJ14" t="n">
         <v>0</v>
@@ -8178,79 +8178,79 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0.02553801593473321</v>
+        <v>-0.07552734939493638</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.03865860001297722</v>
+        <v>0.02130745326117251</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.08059878124067203</v>
+        <v>-0.01263760687469114</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0.03057830847219872</v>
+        <v>0.007701592230680673</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.02619243729951997</v>
+        <v>-0.005106664206720535</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.02979632934395841</v>
+        <v>-0.010902784612389</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0.03790396196512209</v>
+        <v>-0.09824310310737909</v>
       </c>
       <c r="EG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.00812169903954393</v>
+        <v>0.09832822673705081</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.002595699955930855</v>
+        <v>0.01050429385506233</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8259,22 +8259,22 @@
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0.01529973682800669</v>
+        <v>0.03478941032003682</v>
       </c>
       <c r="EP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ14" t="n">
         <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.03378678259352468</v>
+        <v>0.1384870308476897</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.003746849102695152</v>
+        <v>0.001125533422136035</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
@@ -8286,19 +8286,19 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0.03421373231961227</v>
+        <v>-0.06763122327769286</v>
       </c>
       <c r="EY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.008992436127871475</v>
+        <v>0.1584195273580794</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.03612083700315429</v>
+        <v>-0.04015520613218932</v>
       </c>
       <c r="FC14" t="n">
         <v>0</v>
@@ -8310,10 +8310,10 @@
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.002836140414838229</v>
+        <v>0.03832153186499044</v>
       </c>
       <c r="FH14" t="n">
         <v>0</v>
@@ -8322,25 +8322,25 @@
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.01319877608197048</v>
+        <v>0.1294019439214459</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.1215513789028884</v>
+        <v>0.1183313390603556</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
         <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.01261423274869531</v>
+        <v>-0.003919507644915285</v>
       </c>
       <c r="FQ14" t="n">
         <v>-0</v>
@@ -8349,40 +8349,40 @@
         <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.001491104576589455</v>
+        <v>0.2597925146339439</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.04911029474173853</v>
+        <v>0.04884986276619438</v>
       </c>
       <c r="FU14" t="n">
         <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
         <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.02150251150644242</v>
+        <v>0.02934259410116799</v>
       </c>
       <c r="FZ14" t="n">
         <v>0</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.02436690417023375</v>
+        <v>0.2226689116898729</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
@@ -8391,7 +8391,7 @@
         <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -9537,49 +9537,49 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4798839090221421</v>
+        <v>0.09781335023102454</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.08739983253848428</v>
+        <v>-0.05356516483728394</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09708317245157393</v>
+        <v>-0.02696676208968503</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3060445113342578</v>
+        <v>0.1189157520509654</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1350739504912112</v>
+        <v>-0.08893703225860895</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1071874458000956</v>
+        <v>-0.07927083328176937</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -9591,70 +9591,70 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08637900757558158</v>
+        <v>0.02621841888448643</v>
       </c>
       <c r="U17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.03067475875928937</v>
+        <v>-0.0242807791456515</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1364408273779457</v>
+        <v>-0.02213579554419083</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.08478549621922067</v>
+        <v>-0.006480965362691084</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.03401267868909055</v>
+        <v>-0.08646441662069314</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.04946780163147248</v>
+        <v>-0.07482000844443749</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.02788074677289032</v>
+        <v>0.06423320975726951</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.03198605229156495</v>
+        <v>-0.05096219480844606</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.007508879044618359</v>
+        <v>0.03153403222681542</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
@@ -9663,34 +9663,34 @@
         <v>-0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.347499857733591</v>
+        <v>0.1206287412802079</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.258758525554364e-10</v>
+        <v>-8.75565864546064e-12</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1068424098300194</v>
+        <v>-0.1210802734723876</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>-0</v>
@@ -9699,25 +9699,25 @@
         <v>-0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.04515492095906791</v>
+        <v>-0.02010081856790463</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.1920996426943725</v>
+        <v>-0.03640814720156724</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.1484162654406598</v>
+        <v>-0.02375498659037251</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,16 +9726,16 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.1065096399426149</v>
+        <v>0.0408905623672351</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>-0.01319023133283461</v>
+        <v>0.03477881622612052</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.1604846170122597</v>
+        <v>0.04716300015388619</v>
       </c>
       <c r="BQ17" t="n">
         <v>-0</v>
@@ -9747,76 +9747,76 @@
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.1712898781336678</v>
+        <v>0.09677934211594277</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.08290813412540324</v>
+        <v>-0.03948292081902184</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.08901966590799887</v>
+        <v>-0.0264167518776986</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.08712596943517655</v>
+        <v>-0.02676799093335626</v>
       </c>
       <c r="CF17" t="n">
         <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>-0.02075387597562721</v>
+        <v>0.04205193001518072</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.002153592644940722</v>
+        <v>0.0238498129406562</v>
       </c>
       <c r="CI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.009864816534725694</v>
+        <v>-0.05938086061811994</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.1467870035899039</v>
+        <v>0.1101220236548168</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.0920787933183824</v>
+        <v>0.0705938637480866</v>
       </c>
       <c r="CR17" t="n">
         <v>0</v>
@@ -9831,46 +9831,46 @@
         <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.05791724556515188</v>
+        <v>-0.01820059613746765</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.005182475415450661</v>
+        <v>0.04466092199792888</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.009156336064185575</v>
+        <v>0.03033653692151704</v>
       </c>
       <c r="DA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.05148853160773132</v>
+        <v>0.013549590805553</v>
       </c>
       <c r="DG17" t="n">
         <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.05085688338474276</v>
+        <v>-0.004935619158459729</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.05731869786103624</v>
+        <v>-0.04702293530910167</v>
       </c>
       <c r="DJ17" t="n">
         <v>-0</v>
@@ -9885,19 +9885,19 @@
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.06921948725479179</v>
+        <v>-0.05096934750060964</v>
       </c>
       <c r="DP17" t="n">
         <v>0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.003288009373436834</v>
+        <v>-0.027779410375552</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.0501321460496245</v>
+        <v>0.01342096848859628</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -9906,7 +9906,7 @@
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
         <v>0</v>
@@ -9915,16 +9915,16 @@
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.03861324932848842</v>
+        <v>0.005294199331168553</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.03957069134164235</v>
+        <v>0.0287066719788586</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.01956103109405261</v>
+        <v>0.008704220890404176</v>
       </c>
       <c r="EB17" t="n">
         <v>-0</v>
@@ -9933,52 +9933,52 @@
         <v>0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.07212848662979884</v>
+        <v>0.01297632738639439</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>-0.02466539543301993</v>
+        <v>0.02199403092799864</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.0880462334578923</v>
+        <v>0.05371389451692393</v>
       </c>
       <c r="EK17" t="n">
         <v>0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.002182189181602288</v>
+        <v>-0.001602677021559571</v>
       </c>
       <c r="EQ17" t="n">
         <v>0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.01246032849560602</v>
+        <v>0.03711416003971459</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.02266190414171212</v>
+        <v>-0.01254368410268342</v>
       </c>
       <c r="ET17" t="n">
         <v>0</v>
@@ -9990,22 +9990,22 @@
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.05761992190603876</v>
+        <v>-0.02450219310320065</v>
       </c>
       <c r="EZ17" t="n">
         <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>-0.02902193069762792</v>
+        <v>0.05928252199841839</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.01034691459685499</v>
+        <v>0.01677992134610695</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
@@ -10014,85 +10014,85 @@
         <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.004955513465100514</v>
+        <v>0.02994071039930106</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>-0.007035758394658607</v>
+        <v>0.01559399620951297</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.005592818130360866</v>
+        <v>0.01353394389337711</v>
       </c>
       <c r="FL17" t="n">
         <v>-0</v>
       </c>
       <c r="FM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.0419248616880936</v>
+        <v>0.01303524553380487</v>
       </c>
       <c r="FR17" t="n">
         <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.03124223524113894</v>
+        <v>0.02622348904660303</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.03073948573563783</v>
+        <v>-0.0550588781792862</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV17" t="n">
         <v>0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.03075002026424319</v>
+        <v>0.02088309685760888</v>
       </c>
       <c r="GA17" t="n">
         <v>-0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.101573470512779</v>
+        <v>-0.007907131696458528</v>
       </c>
       <c r="GC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
         <v>0</v>
